--- a/output/pdf_financials_xlsx/VOLT.xlsx
+++ b/output/pdf_financials_xlsx/VOLT.xlsx
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.117158</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.255852</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.531879</v>
       </c>
     </row>
     <row r="35">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.116</v>
+        <v>0.233158</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.052</v>
+        <v>0.307852</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.104</v>
+        <v>0.635879</v>
       </c>
     </row>
     <row r="37">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/VOLT.xlsx
+++ b/output/pdf_financials_xlsx/VOLT.xlsx
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.114203</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.281753</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.017517</v>
+        <v>-0.13172</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.187624</v>
+        <v>0.094129</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.07424600000000001</v>
@@ -4703,7 +4703,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>-0.114203</v>
       </c>
